--- a/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_JARINGAN USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/8Juli2026/Agregat_PCL_JARINGAN USAHA.xlsx
@@ -685,13 +685,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="N2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -715,16 +715,16 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="X2" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Y2" t="n">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="Z2" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ2" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="AK2" t="n">
         <v>384</v>
@@ -822,19 +822,19 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="N3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -846,31 +846,31 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="X3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="Y3" t="n">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="Z3" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -882,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ3" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="n">
         <v>354</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="N4" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="O4" t="n">
         <v>2</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -983,31 +983,31 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="X4" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="Y4" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="Z4" t="n">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="AA4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1019,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AJ4" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="AK4" t="n">
         <v>336</v>
@@ -1096,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="N5" t="n">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1126,19 +1126,19 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="X5" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="Y5" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="Z5" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AA5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1162,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ5" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AK5" t="n">
         <v>288</v>
@@ -1233,22 +1233,22 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="N6" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1263,28 +1263,28 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="X6" t="n">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="Y6" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="Z6" t="n">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AJ6" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="AK6" t="n">
         <v>303</v>
@@ -1499,19 +1499,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N8" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1523,31 +1523,31 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="X8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Y8" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z8" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="AA8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ8" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AK8" t="n">
         <v>324</v>
@@ -1639,19 +1639,19 @@
         <v>238</v>
       </c>
       <c r="N9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1666,28 +1666,28 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="X9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Y9" t="n">
         <v>238</v>
       </c>
       <c r="Z9" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="AA9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1702,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AJ9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AK9" t="n">
         <v>379</v>
@@ -1773,19 +1773,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="N10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1803,25 +1803,25 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="X10" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="Y10" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="Z10" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="AA10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ10" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AK10" t="n">
         <v>373</v>
@@ -1910,13 +1910,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="N11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1934,25 +1934,25 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="X11" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="Y11" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="Z11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>435</v>
       </c>
       <c r="AJ11" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AK11" t="n">
         <v>383</v>
@@ -2047,16 +2047,16 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="N12" t="n">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2077,25 +2077,25 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="X12" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="Y12" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="Z12" t="n">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2113,10 +2113,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AJ12" t="n">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="AK12" t="n">
         <v>373</v>
@@ -2184,19 +2184,19 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="N13" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2208,31 +2208,31 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="X13" t="n">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="Y13" t="n">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="Z13" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2244,16 +2244,16 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ13" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AK13" t="n">
         <v>364</v>
@@ -2321,19 +2321,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="N14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="O14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2351,25 +2351,25 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="X14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="Z14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="AA14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AJ14" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="AK14" t="n">
         <v>359</v>
@@ -2458,16 +2458,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="N15" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>398</v>
       </c>
       <c r="X15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="Z15" t="n">
         <v>161</v>
       </c>
       <c r="AA15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
         <v>398</v>
       </c>
       <c r="AJ15" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AK15" t="n">
         <v>367</v>
@@ -2595,22 +2595,22 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="N16" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2619,34 +2619,34 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="X16" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z16" t="n">
         <v>226</v>
       </c>
-      <c r="Y16" t="n">
-        <v>213</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>215</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
         <v>6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2655,16 +2655,16 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AJ16" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="AK16" t="n">
         <v>370</v>
@@ -2732,19 +2732,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="N17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="O17" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2762,25 +2762,25 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="X17" t="n">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="Y17" t="n">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="Z17" t="n">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AA17" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2798,10 +2798,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AJ17" t="n">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="AK17" t="n">
         <v>366</v>
@@ -2869,16 +2869,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="N18" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="O18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2893,25 +2893,25 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="X18" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="Y18" t="n">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="Z18" t="n">
         <v>170</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ18" t="n">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="AK18" t="n">
         <v>423</v>
@@ -3006,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="N19" t="n">
         <v>227</v>
       </c>
       <c r="O19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="X19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="Y19" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z19" t="n">
         <v>227</v>
       </c>
       <c r="AA19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3066,16 +3066,16 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AH19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="AJ19" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AK19" t="n">
         <v>371</v>
@@ -3143,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N20" t="n">
         <v>217</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -3176,16 +3176,16 @@
         <v>298</v>
       </c>
       <c r="X20" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="Y20" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Z20" t="n">
         <v>217</v>
       </c>
       <c r="AA20" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>298</v>
       </c>
       <c r="AJ20" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AK20" t="n">
         <v>284</v>
@@ -3280,13 +3280,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N21" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>401</v>
       </c>
       <c r="X21" t="n">
+        <v>181</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>220</v>
+      </c>
+      <c r="Z21" t="n">
         <v>177</v>
       </c>
-      <c r="Y21" t="n">
-        <v>224</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>165</v>
-      </c>
       <c r="AA21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
         <v>401</v>
       </c>
       <c r="AJ21" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AK21" t="n">
         <v>367</v>
@@ -3417,19 +3417,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="N22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="O22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3447,25 +3447,25 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="X22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="Y22" t="n">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="Z22" t="n">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="AA22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="AJ22" t="n">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="AK22" t="n">
         <v>450</v>
@@ -3554,19 +3554,19 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="N23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="O23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3584,25 +3584,25 @@
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="X23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="Y23" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="Z23" t="n">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="AA23" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>1</v>
       </c>
       <c r="AI23" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AJ23" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="AK23" t="n">
         <v>308</v>
@@ -3691,19 +3691,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="N24" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3721,26 +3721,26 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="X24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="Y24" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="Z24" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AA24" t="n">
         <v>25</v>
       </c>
       <c r="AB24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3</v>
       </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
@@ -3757,10 +3757,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="AJ24" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="AK24" t="n">
         <v>386</v>
@@ -3828,19 +3828,19 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="N25" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3858,25 +3858,25 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="X25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="Y25" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="Z25" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AC25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3894,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AJ25" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AK25" t="n">
         <v>396</v>
@@ -3965,19 +3965,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="N26" t="n">
         <v>170</v>
       </c>
       <c r="O26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3995,25 +3995,25 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="X26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="Y26" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="Z26" t="n">
         <v>170</v>
       </c>
       <c r="AA26" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -4031,10 +4031,10 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AJ26" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AK26" t="n">
         <v>282</v>
@@ -4102,13 +4102,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="N27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -4132,19 +4132,19 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="X27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="Y27" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="Z27" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="AA27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4168,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AJ27" t="n">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="AK27" t="n">
         <v>363</v>
@@ -4239,19 +4239,19 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="N28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -4263,31 +4263,31 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="X28" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="Y28" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Z28" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AA28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4299,16 +4299,16 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AJ28" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="AK28" t="n">
         <v>384</v>
@@ -4376,19 +4376,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="N29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -4406,16 +4406,16 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="X29" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="Y29" t="n">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="Z29" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4442,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AJ29" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="AK29" t="n">
         <v>357</v>
@@ -4516,13 +4516,13 @@
         <v>10</v>
       </c>
       <c r="N30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -4543,22 +4543,22 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="X30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4579,10 +4579,10 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AJ30" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AK30" t="n">
         <v>315</v>
@@ -4650,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -4680,19 +4680,19 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="X31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="Y31" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="Z31" t="n">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="AA31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4716,10 +4716,10 @@
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AJ31" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AK31" t="n">
         <v>366</v>
@@ -4787,19 +4787,19 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="N32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4811,31 +4811,31 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="V32" t="n">
         <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="X32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="Y32" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="Z32" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4847,16 +4847,16 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AH32" t="n">
         <v>1</v>
       </c>
       <c r="AI32" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AJ32" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AK32" t="n">
         <v>455</v>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N34" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -5085,22 +5085,22 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="X34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="Y34" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Z34" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5121,16 +5121,16 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AJ34" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AK34" t="n">
         <v>290</v>
@@ -5198,22 +5198,22 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="N35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="O35" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -5228,22 +5228,22 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="X35" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="Z35" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="AA35" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="AB35" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5264,10 +5264,10 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AJ35" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AK35" t="n">
         <v>372</v>
@@ -5335,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
         <v>2</v>
@@ -5368,16 +5368,16 @@
         <v>491</v>
       </c>
       <c r="X36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="Y36" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="Z36" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB36" t="n">
         <v>2</v>
@@ -5404,7 +5404,7 @@
         <v>491</v>
       </c>
       <c r="AJ36" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AK36" t="n">
         <v>453</v>
@@ -5472,19 +5472,19 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="N37" t="n">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="O37" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5502,26 +5502,26 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="X37" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="Y37" t="n">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="Z37" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="AA37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC37" t="n">
         <v>18</v>
       </c>
-      <c r="AB37" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>25</v>
-      </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
@@ -5538,10 +5538,10 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AJ37" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="AK37" t="n">
         <v>445</v>
@@ -5609,19 +5609,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="N38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5639,19 +5639,19 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X38" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="Y38" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Z38" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ38" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AK38" t="n">
         <v>379</v>
@@ -5746,19 +5746,19 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="N39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -5770,31 +5770,31 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="X39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="Y39" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="Z39" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="AA39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AC39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5806,16 +5806,16 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AJ39" t="n">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="AK39" t="n">
         <v>410</v>
@@ -5883,16 +5883,16 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="N40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -5916,19 +5916,19 @@
         <v>395</v>
       </c>
       <c r="X40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="Y40" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="Z40" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
         <v>395</v>
       </c>
       <c r="AJ40" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="AK40" t="n">
         <v>378</v>
@@ -6020,19 +6020,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="O41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -6050,25 +6050,25 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Y41" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="Z41" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AA41" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -6086,10 +6086,10 @@
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ41" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="AK41" t="n">
         <v>331</v>
@@ -6157,19 +6157,19 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="N42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -6187,25 +6187,25 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="X42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="Y42" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="Z42" t="n">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="AA42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AJ42" t="n">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="AK42" t="n">
         <v>301</v>
@@ -6294,16 +6294,16 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="O43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -6324,22 +6324,22 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="X43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Y43" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Z43" t="n">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="AA43" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AB43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6360,10 +6360,10 @@
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AJ43" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="AK43" t="n">
         <v>371</v>
@@ -6431,10 +6431,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>277</v>
+        <v>545</v>
       </c>
       <c r="N44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -6446,7 +6446,7 @@
         <v>15</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -6455,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>385</v>
+        <v>653</v>
       </c>
       <c r="X44" t="n">
         <v>102</v>
@@ -6470,7 +6470,7 @@
         <v>277</v>
       </c>
       <c r="Z44" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="n">
         <v>1</v>
@@ -6482,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
         <v>0</v>
@@ -6568,31 +6568,31 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="N45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="O45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6601,34 +6601,34 @@
         <v>461</v>
       </c>
       <c r="X45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="Y45" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="Z45" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="AA45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB45" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AC45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>461</v>
       </c>
       <c r="AJ45" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AK45" t="n">
         <v>434</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="N46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -6738,19 +6738,19 @@
         <v>400</v>
       </c>
       <c r="X46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Y46" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="Z46" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="AA46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6774,7 +6774,7 @@
         <v>400</v>
       </c>
       <c r="AJ46" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AK46" t="n">
         <v>375</v>
@@ -6842,13 +6842,13 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="N47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="O47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -6875,16 +6875,16 @@
         <v>449</v>
       </c>
       <c r="X47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="Y47" t="n">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="Z47" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AA47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>449</v>
       </c>
       <c r="AJ47" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AK47" t="n">
         <v>411</v>
@@ -6979,16 +6979,16 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="N48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="O48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="X48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="Y48" t="n">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="Z48" t="n">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="AA48" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -7045,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AJ48" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="AK48" t="n">
         <v>363</v>
@@ -7116,19 +7116,19 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="N49" t="n">
-        <v>216</v>
+        <v>247</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -7146,25 +7146,25 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="X49" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="Y49" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="Z49" t="n">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="AA49" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -7182,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AJ49" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AK49" t="n">
         <v>356</v>
@@ -7253,13 +7253,13 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="N50" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -7271,31 +7271,31 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="X50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="Y50" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="Z50" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="AA50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
@@ -7307,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7319,10 +7319,10 @@
         <v>1</v>
       </c>
       <c r="AI50" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AJ50" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AK50" t="n">
         <v>372</v>
@@ -7390,19 +7390,19 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="N51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -7420,25 +7420,25 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="X51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="Y51" t="n">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="Z51" t="n">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="AA51" t="n">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AC51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -7456,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AJ51" t="n">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="AK51" t="n">
         <v>395</v>
@@ -7527,19 +7527,19 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="N52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="O52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -7551,31 +7551,31 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="X52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Y52" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="Z52" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="AA52" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -7587,16 +7587,16 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH52" t="n">
         <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AJ52" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="AK52" t="n">
         <v>378</v>
@@ -7664,19 +7664,19 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="N53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7694,25 +7694,25 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="X53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="Y53" t="n">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="Z53" t="n">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AC53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -7730,10 +7730,10 @@
         <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="AJ53" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="AK53" t="n">
         <v>507</v>
@@ -7801,19 +7801,19 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="O54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7831,25 +7831,25 @@
         <v>1</v>
       </c>
       <c r="W54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="X54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="Y54" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="Z54" t="n">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="AA54" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
         <v>0</v>
@@ -7867,10 +7867,10 @@
         <v>1</v>
       </c>
       <c r="AI54" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AJ54" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="AK54" t="n">
         <v>407</v>
@@ -7938,13 +7938,13 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N55" t="n">
         <v>156</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -7968,19 +7968,19 @@
         <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="X55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="Y55" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Z55" t="n">
         <v>156</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -8004,10 +8004,10 @@
         <v>1</v>
       </c>
       <c r="AI55" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AJ55" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="AK55" t="n">
         <v>308</v>
@@ -8075,13 +8075,13 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="N56" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="O56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -8105,28 +8105,28 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="X56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="Y56" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="Z56" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="AA56" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AJ56" t="n">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="AK56" t="n">
         <v>363</v>
@@ -8212,16 +8212,16 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N57" t="n">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="O57" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -8242,22 +8242,22 @@
         <v>1</v>
       </c>
       <c r="W57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="X57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="Y57" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="Z57" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="AA57" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AB57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -8278,10 +8278,10 @@
         <v>1</v>
       </c>
       <c r="AI57" t="n">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AJ57" t="n">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AK57" t="n">
         <v>383</v>
@@ -8349,16 +8349,16 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="N58" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="O58" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="P58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q58" t="n">
         <v>7</v>
@@ -8373,31 +8373,31 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V58" t="n">
         <v>1</v>
       </c>
       <c r="W58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="X58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="Y58" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="Z58" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AA58" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AB58" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC58" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
@@ -8409,16 +8409,16 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AH58" t="n">
         <v>1</v>
       </c>
       <c r="AI58" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AJ58" t="n">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="AK58" t="n">
         <v>419</v>
@@ -8486,16 +8486,16 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="N59" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="O59" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -8516,22 +8516,22 @@
         <v>1</v>
       </c>
       <c r="W59" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="X59" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="Y59" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="Z59" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8552,10 +8552,10 @@
         <v>1</v>
       </c>
       <c r="AI59" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AJ59" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AK59" t="n">
         <v>314</v>
@@ -8623,19 +8623,19 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="N60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="O60" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -8653,25 +8653,25 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="X60" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Y60" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="Z60" t="n">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="AA60" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -8689,10 +8689,10 @@
         <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AJ60" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="AK60" t="n">
         <v>365</v>
@@ -8760,19 +8760,19 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="N61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="O61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -8790,25 +8790,25 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="X61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="Y61" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="Z61" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="AA61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -8826,10 +8826,10 @@
         <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ61" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AK61" t="n">
         <v>365</v>
@@ -8897,16 +8897,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="N62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="O62" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -8927,22 +8927,22 @@
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="X62" t="n">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="Y62" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="Z62" t="n">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="AA62" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="AB62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8963,10 +8963,10 @@
         <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="AJ62" t="n">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="AK62" t="n">
         <v>405</v>
@@ -9034,13 +9034,13 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="N63" t="n">
         <v>191</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -9064,19 +9064,19 @@
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="X63" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="Y63" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Z63" t="n">
         <v>191</v>
       </c>
       <c r="AA63" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AJ63" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AK63" t="n">
         <v>417</v>
@@ -9171,19 +9171,19 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="N64" t="n">
         <v>164</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -9201,19 +9201,19 @@
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="X64" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="Y64" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="Z64" t="n">
         <v>164</v>
       </c>
       <c r="AA64" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -9237,10 +9237,10 @@
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AJ64" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="AK64" t="n">
         <v>303</v>
@@ -9308,22 +9308,22 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="N65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="O65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -9338,28 +9338,28 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="X65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Y65" t="n">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="Z65" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AA65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -9374,10 +9374,10 @@
         <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AJ65" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AK65" t="n">
         <v>373</v>
@@ -9445,16 +9445,16 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="N66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="O66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="P66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -9475,22 +9475,22 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="X66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Y66" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Z66" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AA66" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="AB66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -9511,10 +9511,10 @@
         <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AJ66" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AK66" t="n">
         <v>317</v>
@@ -9719,19 +9719,19 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="N68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -9749,25 +9749,25 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="X68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="Y68" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="Z68" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="AA68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AB68" t="n">
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -9785,10 +9785,10 @@
         <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AJ68" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="n">
         <v>278</v>
@@ -9859,16 +9859,16 @@
         <v>239</v>
       </c>
       <c r="N69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
@@ -9895,16 +9895,16 @@
         <v>239</v>
       </c>
       <c r="Z69" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH69" t="n">
         <v>1</v>
@@ -9993,19 +9993,19 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="N70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -10023,25 +10023,25 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="X70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="Y70" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="Z70" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="AA70" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AB70" t="n">
         <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -10059,10 +10059,10 @@
         <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AJ70" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AK70" t="n">
         <v>359</v>
@@ -10130,19 +10130,19 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="O71" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -10160,25 +10160,25 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="X71" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="Y71" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z71" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="AA71" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -10196,10 +10196,10 @@
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AJ71" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK71" t="n">
         <v>357</v>
@@ -10267,13 +10267,13 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="N72" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="O72" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -10297,25 +10297,25 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="X72" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="Y72" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="Z72" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="AA72" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10333,10 +10333,10 @@
         <v>0</v>
       </c>
       <c r="AI72" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AJ72" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AK72" t="n">
         <v>319</v>
@@ -10404,19 +10404,19 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="N73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="O73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -10434,25 +10434,25 @@
         <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="X73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="Y73" t="n">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="Z73" t="n">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="AA73" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD73" t="n">
         <v>0</v>
@@ -10470,10 +10470,10 @@
         <v>0</v>
       </c>
       <c r="AI73" t="n">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AJ73" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="AK73" t="n">
         <v>350</v>
@@ -10541,16 +10541,16 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="N74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="O74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -10571,22 +10571,22 @@
         <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="X74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="Y74" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="Z74" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AA74" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10607,10 +10607,10 @@
         <v>0</v>
       </c>
       <c r="AI74" t="n">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="AJ74" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="AK74" t="n">
         <v>395</v>
@@ -10678,25 +10678,25 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="N75" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="O75" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
@@ -10708,31 +10708,31 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="X75" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="Y75" t="n">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="Z75" t="n">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="AA75" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AB75" t="n">
         <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
@@ -10744,10 +10744,10 @@
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AJ75" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="AK75" t="n">
         <v>263</v>
@@ -10815,25 +10815,25 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="N76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
         <v>0</v>
@@ -10845,31 +10845,31 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="X76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="Y76" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="Z76" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AA76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD76" t="n">
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
@@ -10881,10 +10881,10 @@
         <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AJ76" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AK76" t="n">
         <v>342</v>
@@ -10952,10 +10952,10 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10964,13 +10964,13 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
         <v>0</v>
@@ -10982,16 +10982,16 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="X77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="Y77" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="Z77" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -11000,13 +11000,13 @@
         <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD77" t="n">
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
@@ -11018,10 +11018,10 @@
         <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AJ77" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="AK77" t="n">
         <v>313</v>
@@ -11089,13 +11089,13 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="N78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="O78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -11113,25 +11113,25 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="X78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="Y78" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="Z78" t="n">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AA78" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
@@ -11149,16 +11149,16 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH78" t="n">
         <v>0</v>
       </c>
       <c r="AI78" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AJ78" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="AK78" t="n">
         <v>385</v>
@@ -11226,13 +11226,13 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="N79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
@@ -11250,25 +11250,25 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="X79" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="Y79" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="Z79" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="AA79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB79" t="n">
         <v>1</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AH79" t="n">
         <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AJ79" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AK79" t="n">
         <v>419</v>
@@ -11363,13 +11363,13 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N80" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="O80" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -11387,25 +11387,25 @@
         <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="X80" t="n">
+        <v>206</v>
+      </c>
+      <c r="Y80" t="n">
         <v>199</v>
       </c>
-      <c r="Y80" t="n">
-        <v>201</v>
-      </c>
       <c r="Z80" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AA80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -11423,16 +11423,16 @@
         <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AH80" t="n">
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AJ80" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AK80" t="n">
         <v>324</v>
@@ -11500,25 +11500,25 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="N81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="O81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="P81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
         <v>0</v>
@@ -11530,31 +11530,31 @@
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="X81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="Y81" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="Z81" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="AA81" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AB81" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AC81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF81" t="n">
         <v>0</v>
@@ -11566,10 +11566,10 @@
         <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AJ81" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="AK81" t="n">
         <v>378</v>
@@ -11637,13 +11637,13 @@
         <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="N82" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -11670,16 +11670,16 @@
         <v>383</v>
       </c>
       <c r="X82" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="Y82" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="Z82" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="AA82" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AB82" t="n">
         <v>0</v>
@@ -11703,10 +11703,10 @@
         <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AJ82" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AK82" t="n">
         <v>367</v>
@@ -11774,16 +11774,16 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="N83" t="n">
         <v>125</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q83" t="n">
         <v>12</v>
@@ -11804,22 +11804,22 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="X83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="Y83" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="Z83" t="n">
         <v>125</v>
       </c>
       <c r="AA83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AB83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC83" t="n">
         <v>12</v>
@@ -11840,10 +11840,10 @@
         <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AJ83" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="AK83" t="n">
         <v>360</v>
@@ -11911,19 +11911,19 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="N84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="O84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -11941,25 +11941,25 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="X84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="Y84" t="n">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="Z84" t="n">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="AA84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -11977,10 +11977,10 @@
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AJ84" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="AK84" t="n">
         <v>356</v>
@@ -12051,13 +12051,13 @@
         <v>146</v>
       </c>
       <c r="N85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -12081,19 +12081,19 @@
         <v>323</v>
       </c>
       <c r="X85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="Y85" t="n">
         <v>146</v>
       </c>
       <c r="Z85" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -12117,7 +12117,7 @@
         <v>323</v>
       </c>
       <c r="AJ85" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AK85" t="n">
         <v>301</v>
@@ -12185,13 +12185,13 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="N86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="O86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -12209,7 +12209,7 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -12218,16 +12218,16 @@
         <v>420</v>
       </c>
       <c r="X86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="Y86" t="n">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="Z86" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AA86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AB86" t="n">
         <v>0</v>
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="n">
         <v>0</v>
@@ -12254,7 +12254,7 @@
         <v>420</v>
       </c>
       <c r="AJ86" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="AK86" t="n">
         <v>399</v>
@@ -12322,16 +12322,16 @@
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="O87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -12346,28 +12346,28 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V87" t="n">
         <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="X87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="Y87" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="Z87" t="n">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="AA87" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -12382,16 +12382,16 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH87" t="n">
         <v>0</v>
       </c>
       <c r="AI87" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AJ87" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="AK87" t="n">
         <v>366</v>
@@ -12459,20 +12459,20 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="N88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q88" t="n">
         <v>6</v>
       </c>
-      <c r="Q88" t="n">
-        <v>1</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -12483,32 +12483,32 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="X88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="Y88" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Z88" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AA88" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AB88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC88" t="n">
         <v>6</v>
       </c>
-      <c r="AC88" t="n">
-        <v>1</v>
-      </c>
       <c r="AD88" t="n">
         <v>0</v>
       </c>
@@ -12519,16 +12519,16 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="n">
         <v>0</v>
       </c>
       <c r="AI88" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AJ88" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AK88" t="n">
         <v>364</v>
@@ -12596,13 +12596,13 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="N89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -12620,25 +12620,25 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="X89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="Y89" t="n">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="Z89" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AA89" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AB89" t="n">
         <v>0</v>
@@ -12656,16 +12656,16 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH89" t="n">
         <v>0</v>
       </c>
       <c r="AI89" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AJ89" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="AK89" t="n">
         <v>440</v>
@@ -12733,13 +12733,13 @@
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="O90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -12757,7 +12757,7 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
@@ -12766,16 +12766,16 @@
         <v>386</v>
       </c>
       <c r="X90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y90" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="Z90" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="AA90" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
@@ -12793,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AH90" t="n">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>386</v>
       </c>
       <c r="AJ90" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AK90" t="n">
         <v>335</v>
@@ -12870,76 +12870,76 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="N91" t="n">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P91" t="n">
         <v>4</v>
       </c>
       <c r="Q91" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="X91" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="Y91" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="Z91" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="AA91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB91" t="n">
         <v>4</v>
       </c>
       <c r="AC91" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF91" t="n">
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="AH91" t="n">
         <v>0</v>
       </c>
       <c r="AI91" t="n">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AJ91" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="AK91" t="n">
         <v>430</v>
@@ -13007,19 +13007,19 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="N92" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -13037,25 +13037,25 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="X92" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="Y92" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="Z92" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AA92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB92" t="n">
         <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -13073,10 +13073,10 @@
         <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AJ92" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AK92" t="n">
         <v>343</v>
@@ -13144,19 +13144,19 @@
         <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="N93" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="O93" t="n">
         <v>2</v>
       </c>
       <c r="P93" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="Q93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
@@ -13174,25 +13174,25 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="X93" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Y93" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="Z93" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="AA93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD93" t="n">
         <v>0</v>
@@ -13210,10 +13210,10 @@
         <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AJ93" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AK93" t="n">
         <v>364</v>
@@ -13281,16 +13281,16 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="N94" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -13305,28 +13305,28 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="X94" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="Y94" t="n">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="Z94" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="AA94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB94" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -13341,16 +13341,16 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI94" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AJ94" t="n">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="AK94" t="n">
         <v>437</v>
@@ -13418,19 +13418,19 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="N95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="O95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -13448,25 +13448,25 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="X95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Y95" t="n">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="Z95" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="AA95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AB95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AD95" t="n">
         <v>0</v>
@@ -13484,10 +13484,10 @@
         <v>0</v>
       </c>
       <c r="AI95" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AJ95" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="AK95" t="n">
         <v>472</v>
@@ -13555,19 +13555,19 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="N96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
@@ -13585,25 +13585,25 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="X96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="Y96" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="Z96" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AA96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AD96" t="n">
         <v>0</v>
@@ -13621,10 +13621,10 @@
         <v>0</v>
       </c>
       <c r="AI96" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AJ96" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="AK96" t="n">
         <v>340</v>
@@ -13692,16 +13692,16 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="N97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="O97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="P97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -13716,28 +13716,28 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V97" t="n">
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="X97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="Y97" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="Z97" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AA97" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AB97" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13752,16 +13752,16 @@
         <v>0</v>
       </c>
       <c r="AG97" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AH97" t="n">
         <v>1</v>
       </c>
       <c r="AI97" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="AJ97" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AK97" t="n">
         <v>316</v>
@@ -13829,16 +13829,16 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="N98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="O98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q98" t="n">
         <v>5</v>
@@ -13862,19 +13862,19 @@
         <v>450</v>
       </c>
       <c r="X98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="Y98" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="Z98" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="AA98" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC98" t="n">
         <v>5</v>
@@ -13898,7 +13898,7 @@
         <v>450</v>
       </c>
       <c r="AJ98" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AK98" t="n">
         <v>422</v>
@@ -13966,10 +13966,10 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="O99" t="n">
         <v>3</v>
@@ -13978,7 +13978,7 @@
         <v>5</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -13990,22 +13990,22 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="X99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Y99" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z99" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AA99" t="n">
         <v>3</v>
@@ -14014,7 +14014,7 @@
         <v>5</v>
       </c>
       <c r="AC99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
         <v>0</v>
@@ -14026,16 +14026,16 @@
         <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="AH99" t="n">
         <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AJ99" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AK99" t="n">
         <v>391</v>
@@ -14103,19 +14103,19 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="N100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
@@ -14133,25 +14133,25 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="X100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="Y100" t="n">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="Z100" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="AA100" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB100" t="n">
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AD100" t="n">
         <v>0</v>
@@ -14169,10 +14169,10 @@
         <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AJ100" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="AK100" t="n">
         <v>366</v>
@@ -14240,13 +14240,13 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="N101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="O101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -14264,25 +14264,25 @@
         <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V101" t="n">
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="X101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="Y101" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="Z101" t="n">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="AA101" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AB101" t="n">
         <v>0</v>
@@ -14300,16 +14300,16 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AH101" t="n">
         <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AJ101" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="AK101" t="n">
         <v>335</v>
@@ -14377,22 +14377,22 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="N102" t="n">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -14401,34 +14401,34 @@
         <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V102" t="n">
         <v>1</v>
       </c>
       <c r="W102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="X102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="Y102" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="Z102" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="AA102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -14437,16 +14437,16 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AH102" t="n">
         <v>1</v>
       </c>
       <c r="AI102" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AJ102" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="AK102" t="n">
         <v>398</v>
@@ -14514,19 +14514,19 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="N103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="O103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -14538,25 +14538,25 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V103" t="n">
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="X103" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="Y103" t="n">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="Z103" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="AA103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB103" t="n">
         <v>0</v>
@@ -14574,16 +14574,16 @@
         <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH103" t="n">
         <v>0</v>
       </c>
       <c r="AI103" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AJ103" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="AK103" t="n">
         <v>322</v>
@@ -14651,19 +14651,19 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="N104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
@@ -14675,31 +14675,31 @@
         <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V104" t="n">
         <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="X104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="Y104" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="Z104" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AA104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB104" t="n">
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
@@ -14711,16 +14711,16 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AH104" t="n">
         <v>0</v>
       </c>
       <c r="AI104" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AJ104" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AK104" t="n">
         <v>288</v>
@@ -14788,13 +14788,13 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="O105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P105" t="n">
         <v>2</v>
@@ -14818,19 +14818,19 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="X105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Y105" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="Z105" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AA105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB105" t="n">
         <v>2</v>
@@ -14854,10 +14854,10 @@
         <v>0</v>
       </c>
       <c r="AI105" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AJ105" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AK105" t="n">
         <v>294</v>
@@ -14925,13 +14925,13 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="N106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -14940,10 +14940,10 @@
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
@@ -14958,16 +14958,16 @@
         <v>422</v>
       </c>
       <c r="X106" t="n">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="Y106" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="Z106" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="AA106" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AB106" t="n">
         <v>0</v>
@@ -14976,10 +14976,10 @@
         <v>0</v>
       </c>
       <c r="AD106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF106" t="n">
         <v>0</v>
@@ -14994,7 +14994,7 @@
         <v>422</v>
       </c>
       <c r="AJ106" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="AK106" t="n">
         <v>403</v>
@@ -15062,16 +15062,16 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
@@ -15086,7 +15086,7 @@
         <v>0</v>
       </c>
       <c r="U107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
@@ -15095,19 +15095,19 @@
         <v>481</v>
       </c>
       <c r="X107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Y107" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z107" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AA107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB107" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC107" t="n">
         <v>1</v>
@@ -15122,7 +15122,7 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AH107" t="n">
         <v>0</v>
@@ -15131,7 +15131,7 @@
         <v>481</v>
       </c>
       <c r="AJ107" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AK107" t="n">
         <v>432</v>
@@ -15199,19 +15199,19 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="N108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="O108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -15229,25 +15229,25 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="X108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="Y108" t="n">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="Z108" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="AA108" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AB108" t="n">
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD108" t="n">
         <v>0</v>
@@ -15265,10 +15265,10 @@
         <v>0</v>
       </c>
       <c r="AI108" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AJ108" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="AK108" t="n">
         <v>362</v>
@@ -15336,13 +15336,13 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="N109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -15366,19 +15366,19 @@
         <v>4</v>
       </c>
       <c r="W109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="X109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="Y109" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="Z109" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB109" t="n">
         <v>0</v>
@@ -15402,10 +15402,10 @@
         <v>4</v>
       </c>
       <c r="AI109" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AJ109" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="AK109" t="n">
         <v>412</v>
@@ -15610,16 +15610,16 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="N111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -15640,22 +15640,22 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="X111" t="n">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="Y111" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="Z111" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="AA111" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -15676,10 +15676,10 @@
         <v>0</v>
       </c>
       <c r="AI111" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AJ111" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="AK111" t="n">
         <v>255</v>
@@ -15747,19 +15747,19 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="N112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
         <v>0</v>
@@ -15771,31 +15771,31 @@
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="V112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="X112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="Y112" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="Z112" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AA112" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AB112" t="n">
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD112" t="n">
         <v>0</v>
@@ -15807,16 +15807,16 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AH112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI112" t="n">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AJ112" t="n">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="AK112" t="n">
         <v>382</v>
@@ -15884,19 +15884,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -15914,25 +15914,25 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="X113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Y113" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="Z113" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
         <v>0</v>
@@ -15950,10 +15950,10 @@
         <v>0</v>
       </c>
       <c r="AI113" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AJ113" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="AK113" t="n">
         <v>420</v>
@@ -16021,19 +16021,19 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="N114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="O114" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -16051,25 +16051,25 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="X114" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="Y114" t="n">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Z114" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="AA114" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AB114" t="n">
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD114" t="n">
         <v>0</v>
@@ -16087,10 +16087,10 @@
         <v>0</v>
       </c>
       <c r="AI114" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AJ114" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="AK114" t="n">
         <v>333</v>
@@ -16158,19 +16158,19 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="N115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="O115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -16191,22 +16191,22 @@
         <v>417</v>
       </c>
       <c r="X115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="Y115" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="Z115" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="AA115" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD115" t="n">
         <v>0</v>
@@ -16227,7 +16227,7 @@
         <v>417</v>
       </c>
       <c r="AJ115" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="AK115" t="n">
         <v>364</v>
@@ -16295,19 +16295,19 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="N116" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="O116" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
         <v>0</v>
@@ -16319,34 +16319,34 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V116" t="n">
         <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="X116" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="Y116" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="Z116" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="AA116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC116" t="n">
         <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -16355,16 +16355,16 @@
         <v>0</v>
       </c>
       <c r="AG116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH116" t="n">
         <v>0</v>
       </c>
       <c r="AI116" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="AJ116" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AK116" t="n">
         <v>378</v>
@@ -16432,13 +16432,13 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="N117" t="n">
         <v>178</v>
       </c>
       <c r="O117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="P117" t="n">
         <v>0</v>
@@ -16465,16 +16465,16 @@
         <v>462</v>
       </c>
       <c r="X117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="Y117" t="n">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="Z117" t="n">
         <v>178</v>
       </c>
       <c r="AA117" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AB117" t="n">
         <v>0</v>
@@ -16501,7 +16501,7 @@
         <v>462</v>
       </c>
       <c r="AJ117" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AK117" t="n">
         <v>420</v>
@@ -16569,16 +16569,16 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="N118" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="O118" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="P118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q118" t="n">
         <v>1</v>
@@ -16599,25 +16599,25 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="X118" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="Y118" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Z118" t="n">
         <v>138</v>
       </c>
       <c r="AA118" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="AB118" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC118" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16635,10 +16635,10 @@
         <v>0</v>
       </c>
       <c r="AI118" t="n">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AJ118" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="AK118" t="n">
         <v>336</v>
@@ -16706,13 +16706,13 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="N119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="O119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
@@ -16736,19 +16736,19 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="X119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Y119" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z119" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="AA119" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AB119" t="n">
         <v>0</v>
@@ -16772,10 +16772,10 @@
         <v>0</v>
       </c>
       <c r="AI119" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AJ119" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AK119" t="n">
         <v>344</v>
@@ -16843,19 +16843,19 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="N120" t="n">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="O120" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0</v>
@@ -16867,31 +16867,31 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
+        <v>15</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>500</v>
+      </c>
+      <c r="X120" t="n">
+        <v>364</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>137</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>341</v>
+      </c>
+      <c r="AA120" t="n">
         <v>7</v>
       </c>
-      <c r="V120" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" t="n">
-        <v>488</v>
-      </c>
-      <c r="X120" t="n">
-        <v>344</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>144</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>318</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>18</v>
-      </c>
       <c r="AB120" t="n">
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
         <v>0</v>
@@ -16903,16 +16903,16 @@
         <v>0</v>
       </c>
       <c r="AG120" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AH120" t="n">
         <v>0</v>
       </c>
       <c r="AI120" t="n">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AJ120" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="AK120" t="n">
         <v>353</v>
@@ -16980,13 +16980,13 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="N121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
@@ -17010,19 +17010,19 @@
         <v>1</v>
       </c>
       <c r="W121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="X121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="Y121" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="Z121" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AA121" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB121" t="n">
         <v>0</v>
@@ -17046,10 +17046,10 @@
         <v>1</v>
       </c>
       <c r="AI121" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AJ121" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AK121" t="n">
         <v>321</v>
@@ -17117,13 +17117,13 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="N122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="O122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -17147,16 +17147,16 @@
         <v>1</v>
       </c>
       <c r="W122" t="n">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="X122" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Y122" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Z122" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -17183,10 +17183,10 @@
         <v>1</v>
       </c>
       <c r="AI122" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="AJ122" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="AK122" t="n">
         <v>297</v>
@@ -17254,19 +17254,19 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="N123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="O123" t="n">
         <v>4</v>
       </c>
       <c r="P123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="R123" t="n">
         <v>0</v>
@@ -17284,25 +17284,25 @@
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="X123" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="Y123" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="Z123" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="AA123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AC123" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="AD123" t="n">
         <v>0</v>
@@ -17320,10 +17320,10 @@
         <v>0</v>
       </c>
       <c r="AI123" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AJ123" t="n">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AK123" t="n">
         <v>367</v>
@@ -17391,16 +17391,16 @@
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="N124" t="n">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P124" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -17421,22 +17421,22 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="X124" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="Y124" t="n">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="Z124" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AA124" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB124" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -17457,10 +17457,10 @@
         <v>0</v>
       </c>
       <c r="AI124" t="n">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="AJ124" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AK124" t="n">
         <v>410</v>
@@ -17528,22 +17528,22 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -17552,34 +17552,34 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="X125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="Y125" t="n">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Z125" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AC125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -17588,16 +17588,16 @@
         <v>0</v>
       </c>
       <c r="AG125" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AH125" t="n">
         <v>0</v>
       </c>
       <c r="AI125" t="n">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="AJ125" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="AK125" t="n">
         <v>394</v>
@@ -17665,13 +17665,13 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="N126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="O126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -17695,19 +17695,19 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="X126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="Y126" t="n">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="Z126" t="n">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="AA126" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AB126" t="n">
         <v>0</v>
@@ -17731,10 +17731,10 @@
         <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AJ126" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AK126" t="n">
         <v>324</v>
@@ -17802,19 +17802,19 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="O127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -17832,25 +17832,25 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="X127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="Y127" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="Z127" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="AA127" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AB127" t="n">
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="AI127" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AJ127" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AK127" t="n">
         <v>384</v>
@@ -17939,50 +17939,50 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="N128" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>17</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>494</v>
+      </c>
+      <c r="X128" t="n">
+        <v>261</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>233</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>236</v>
+      </c>
+      <c r="AA128" t="n">
         <v>8</v>
       </c>
-      <c r="R128" t="n">
-        <v>9</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>492</v>
-      </c>
-      <c r="X128" t="n">
-        <v>240</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>246</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>240</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>7</v>
-      </c>
       <c r="AB128" t="n">
         <v>0</v>
       </c>
@@ -17999,16 +17999,16 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH128" t="n">
         <v>0</v>
       </c>
       <c r="AI128" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AJ128" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="AK128" t="n">
         <v>457</v>
@@ -18076,17 +18076,17 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="N129" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="O129" t="n">
+        <v>4</v>
+      </c>
+      <c r="P129" t="n">
         <v>7</v>
       </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
@@ -18100,28 +18100,28 @@
         <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="V129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="X129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="Y129" t="n">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="Z129" t="n">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="AA129" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -18136,16 +18136,16 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AH129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI129" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="AJ129" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AK129" t="n">
         <v>429</v>
@@ -18213,13 +18213,13 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="N130" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="O130" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P130" t="n">
         <v>0</v>
@@ -18243,19 +18243,19 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="X130" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="Y130" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="Z130" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB130" t="n">
         <v>0</v>
@@ -18279,10 +18279,10 @@
         <v>0</v>
       </c>
       <c r="AI130" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AJ130" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="AK130" t="n">
         <v>313</v>
@@ -18350,19 +18350,19 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="N131" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" t="n">
         <v>0</v>
@@ -18380,16 +18380,16 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="X131" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="Y131" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Z131" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>1</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD131" t="n">
         <v>0</v>
@@ -18416,10 +18416,10 @@
         <v>0</v>
       </c>
       <c r="AI131" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AJ131" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AK131" t="n">
         <v>324</v>
@@ -18487,19 +18487,19 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="N132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="O132" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="P132" t="n">
         <v>2</v>
       </c>
       <c r="Q132" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R132" t="n">
         <v>0</v>
@@ -18517,25 +18517,25 @@
         <v>0</v>
       </c>
       <c r="W132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="X132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="Y132" t="n">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="Z132" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="AA132" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AB132" t="n">
         <v>2</v>
       </c>
       <c r="AC132" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AD132" t="n">
         <v>0</v>
@@ -18553,10 +18553,10 @@
         <v>0</v>
       </c>
       <c r="AI132" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AJ132" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="AK132" t="n">
         <v>377</v>
@@ -18624,16 +18624,16 @@
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="N133" t="n">
         <v>163</v>
       </c>
       <c r="O133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="P133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
@@ -18654,22 +18654,22 @@
         <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="X133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Y133" t="n">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="Z133" t="n">
         <v>163</v>
       </c>
       <c r="AA133" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="AB133" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -18690,10 +18690,10 @@
         <v>0</v>
       </c>
       <c r="AI133" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AJ133" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="AK133" t="n">
         <v>386</v>
@@ -18761,16 +18761,16 @@
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="N134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
         <v>5</v>
-      </c>
-      <c r="P134" t="n">
-        <v>1</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
@@ -18794,19 +18794,19 @@
         <v>398</v>
       </c>
       <c r="X134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="Y134" t="n">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="Z134" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="AA134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" t="n">
         <v>5</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>1</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
         <v>398</v>
       </c>
       <c r="AJ134" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="AK134" t="n">
         <v>370</v>
@@ -18898,31 +18898,31 @@
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="N135" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="O135" t="n">
+        <v>11</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
         <v>12</v>
-      </c>
-      <c r="P135" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>5</v>
       </c>
       <c r="V135" t="n">
         <v>0</v>
@@ -18931,19 +18931,19 @@
         <v>414</v>
       </c>
       <c r="X135" t="n">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="Y135" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Z135" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="AA135" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AB135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -18967,7 +18967,7 @@
         <v>414</v>
       </c>
       <c r="AJ135" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="AK135" t="n">
         <v>368</v>
